--- a/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -492,25 +492,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42375.89523809524</v>
+        <v>46427.91428571429</v>
       </c>
       <c r="C2" t="n">
-        <v>446.0620551378447</v>
+        <v>478.6382916053019</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2674.421331092894</v>
+        <v>2548.188196745972</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>24385</v>
+        <v>22383</v>
       </c>
       <c r="H2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I2" t="n">
         <v>106</v>
@@ -519,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46427.91428571429</v>
+        <v>349996.9809523809</v>
       </c>
       <c r="C2" t="n">
-        <v>478.6382916053019</v>
+        <v>3365.355586080586</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2548.188196745972</v>
+        <v>10185.83497680896</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>22383</v>
+        <v>36003</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I2" t="n">
         <v>106</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>SourceTable</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total(s)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean(s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Median(s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Median(min)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Standard Deviation(s)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Minimum(s)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Maximum(s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Completed API Count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>All API Count</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>&gt; 1-Hour</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>&gt; 30-Minutes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_yes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_no</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_unknown</t>
         </is>
       </c>
     </row>
@@ -491,35 +516,52 @@
           <t>freertos-10.5.1</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>349996.9809523809</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>walltime</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>3365.355586080586</v>
+        <v>368425.6809</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3508.816008571428</v>
       </c>
       <c r="E2" t="n">
-        <v>10185.83497680896</v>
+        <v>1.0519</v>
       </c>
       <c r="F2" t="n">
+        <v>0.01753166666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10291.44214788202</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36002.3446</v>
+      </c>
+      <c r="J2" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2" t="n">
+        <v>105</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>36003</v>
-      </c>
-      <c r="H2" t="n">
-        <v>104</v>
-      </c>
-      <c r="I2" t="n">
-        <v>106</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>12</v>
+      <c r="O2" t="n">
+        <v>105</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
